--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647223</v>
+        <v>122647218</v>
       </c>
       <c r="B2" t="n">
-        <v>78738</v>
+        <v>91124</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551477</v>
+        <v>551451</v>
       </c>
       <c r="R2" t="n">
-        <v>7246026</v>
+        <v>7245990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647214</v>
+        <v>122647208</v>
       </c>
       <c r="B3" t="n">
-        <v>74757</v>
+        <v>91616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>918</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551447</v>
+        <v>551419</v>
       </c>
       <c r="R3" t="n">
-        <v>7245973</v>
+        <v>7245952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647207</v>
+        <v>122647213</v>
       </c>
       <c r="B6" t="n">
-        <v>90851</v>
+        <v>90829</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551407</v>
+        <v>551412</v>
       </c>
       <c r="R6" t="n">
-        <v>7245970</v>
+        <v>7245972</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647234</v>
+        <v>122647219</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>90833</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551528</v>
+        <v>551453</v>
       </c>
       <c r="R7" t="n">
-        <v>7246053</v>
+        <v>7245978</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647224</v>
+        <v>122647209</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>82443</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551488</v>
+        <v>551421</v>
       </c>
       <c r="R9" t="n">
-        <v>7246025</v>
+        <v>7245967</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647208</v>
+        <v>122647207</v>
       </c>
       <c r="B10" t="n">
-        <v>91616</v>
+        <v>90851</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>918</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551419</v>
+        <v>551407</v>
       </c>
       <c r="R10" t="n">
-        <v>7245952</v>
+        <v>7245970</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647221</v>
+        <v>122647232</v>
       </c>
       <c r="B11" t="n">
-        <v>90851</v>
+        <v>56593</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551452</v>
+        <v>551496</v>
       </c>
       <c r="R11" t="n">
-        <v>7246015</v>
+        <v>7246066</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,6 +1710,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647232</v>
+        <v>122647214</v>
       </c>
       <c r="B12" t="n">
-        <v>56593</v>
+        <v>74757</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1757,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551496</v>
+        <v>551447</v>
       </c>
       <c r="R12" t="n">
-        <v>7246066</v>
+        <v>7245973</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,11 +1821,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647219</v>
+        <v>122647221</v>
       </c>
       <c r="B14" t="n">
-        <v>90833</v>
+        <v>90851</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551453</v>
+        <v>551452</v>
       </c>
       <c r="R14" t="n">
-        <v>7245978</v>
+        <v>7246015</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647209</v>
+        <v>122647234</v>
       </c>
       <c r="B15" t="n">
-        <v>82443</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,21 +2079,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551421</v>
+        <v>551528</v>
       </c>
       <c r="R15" t="n">
-        <v>7245967</v>
+        <v>7246053</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647218</v>
+        <v>122647224</v>
       </c>
       <c r="B16" t="n">
-        <v>91124</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,21 +2185,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551451</v>
+        <v>551488</v>
       </c>
       <c r="R16" t="n">
-        <v>7245990</v>
+        <v>7246025</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647213</v>
+        <v>122647223</v>
       </c>
       <c r="B17" t="n">
-        <v>90829</v>
+        <v>78738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551412</v>
+        <v>551477</v>
       </c>
       <c r="R17" t="n">
-        <v>7245972</v>
+        <v>7246026</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647218</v>
+        <v>122647219</v>
       </c>
       <c r="B2" t="n">
-        <v>91124</v>
+        <v>90834</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551451</v>
+        <v>551453</v>
       </c>
       <c r="R2" t="n">
-        <v>7245990</v>
+        <v>7245978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647208</v>
+        <v>122647233</v>
       </c>
       <c r="B3" t="n">
-        <v>91616</v>
+        <v>90852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>918</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551419</v>
+        <v>551495</v>
       </c>
       <c r="R3" t="n">
-        <v>7245952</v>
+        <v>7246051</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>122647220</v>
       </c>
       <c r="B4" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647222</v>
+        <v>122647224</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551481</v>
+        <v>551488</v>
       </c>
       <c r="R5" t="n">
-        <v>7246012</v>
+        <v>7246025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,11 +1069,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647213</v>
+        <v>122647214</v>
       </c>
       <c r="B6" t="n">
-        <v>90829</v>
+        <v>74758</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551412</v>
+        <v>551447</v>
       </c>
       <c r="R6" t="n">
-        <v>7245972</v>
+        <v>7245973</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647219</v>
+        <v>122647223</v>
       </c>
       <c r="B7" t="n">
-        <v>90833</v>
+        <v>78739</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551453</v>
+        <v>551477</v>
       </c>
       <c r="R7" t="n">
-        <v>7245978</v>
+        <v>7246026</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647233</v>
+        <v>122647208</v>
       </c>
       <c r="B8" t="n">
-        <v>90851</v>
+        <v>91617</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>918</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551495</v>
+        <v>551419</v>
       </c>
       <c r="R8" t="n">
-        <v>7246051</v>
+        <v>7245952</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,7 +1420,7 @@
         <v>122647209</v>
       </c>
       <c r="B9" t="n">
-        <v>82443</v>
+        <v>82444</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647207</v>
+        <v>122647234</v>
       </c>
       <c r="B10" t="n">
-        <v>90851</v>
+        <v>78657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551407</v>
+        <v>551528</v>
       </c>
       <c r="R10" t="n">
-        <v>7245970</v>
+        <v>7246053</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647232</v>
+        <v>122647218</v>
       </c>
       <c r="B11" t="n">
-        <v>56593</v>
+        <v>91125</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551496</v>
+        <v>551451</v>
       </c>
       <c r="R11" t="n">
-        <v>7246066</v>
+        <v>7245990</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,11 +1705,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647214</v>
+        <v>122647222</v>
       </c>
       <c r="B12" t="n">
-        <v>74757</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551447</v>
+        <v>551481</v>
       </c>
       <c r="R12" t="n">
-        <v>7245973</v>
+        <v>7246012</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,6 +1811,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647225</v>
+        <v>122647221</v>
       </c>
       <c r="B13" t="n">
-        <v>74757</v>
+        <v>90852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551491</v>
+        <v>551452</v>
       </c>
       <c r="R13" t="n">
-        <v>7246031</v>
+        <v>7246015</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647221</v>
+        <v>122647232</v>
       </c>
       <c r="B14" t="n">
-        <v>90851</v>
+        <v>56594</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551452</v>
+        <v>551496</v>
       </c>
       <c r="R14" t="n">
-        <v>7246015</v>
+        <v>7246066</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,6 +2028,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647234</v>
+        <v>122647207</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>90852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,21 +2079,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551528</v>
+        <v>551407</v>
       </c>
       <c r="R15" t="n">
-        <v>7246053</v>
+        <v>7245970</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647224</v>
+        <v>122647225</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>74758</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,21 +2185,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551488</v>
+        <v>551491</v>
       </c>
       <c r="R16" t="n">
-        <v>7246025</v>
+        <v>7246031</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647223</v>
+        <v>122647213</v>
       </c>
       <c r="B17" t="n">
-        <v>78738</v>
+        <v>90830</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551477</v>
+        <v>551412</v>
       </c>
       <c r="R17" t="n">
-        <v>7246026</v>
+        <v>7245972</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647219</v>
+        <v>122647234</v>
       </c>
       <c r="B2" t="n">
-        <v>90834</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551453</v>
+        <v>551528</v>
       </c>
       <c r="R2" t="n">
-        <v>7245978</v>
+        <v>7246053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647233</v>
+        <v>122647223</v>
       </c>
       <c r="B3" t="n">
-        <v>90852</v>
+        <v>78742</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551495</v>
+        <v>551477</v>
       </c>
       <c r="R3" t="n">
-        <v>7246051</v>
+        <v>7246026</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647220</v>
+        <v>122647225</v>
       </c>
       <c r="B4" t="n">
-        <v>78739</v>
+        <v>74761</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551458</v>
+        <v>551491</v>
       </c>
       <c r="R4" t="n">
-        <v>7245993</v>
+        <v>7246031</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>122647224</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647214</v>
+        <v>122647207</v>
       </c>
       <c r="B6" t="n">
-        <v>74758</v>
+        <v>90855</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551447</v>
+        <v>551407</v>
       </c>
       <c r="R6" t="n">
-        <v>7245973</v>
+        <v>7245970</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647223</v>
+        <v>122647220</v>
       </c>
       <c r="B7" t="n">
-        <v>78739</v>
+        <v>78742</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551477</v>
+        <v>551458</v>
       </c>
       <c r="R7" t="n">
-        <v>7246026</v>
+        <v>7245993</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647208</v>
+        <v>122647214</v>
       </c>
       <c r="B8" t="n">
-        <v>91617</v>
+        <v>74761</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>918</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551419</v>
+        <v>551447</v>
       </c>
       <c r="R8" t="n">
-        <v>7245952</v>
+        <v>7245973</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647209</v>
+        <v>122647233</v>
       </c>
       <c r="B9" t="n">
-        <v>82444</v>
+        <v>90855</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551421</v>
+        <v>551495</v>
       </c>
       <c r="R9" t="n">
-        <v>7245967</v>
+        <v>7246051</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647234</v>
+        <v>122647219</v>
       </c>
       <c r="B10" t="n">
-        <v>78657</v>
+        <v>90837</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551528</v>
+        <v>551453</v>
       </c>
       <c r="R10" t="n">
-        <v>7246053</v>
+        <v>7245978</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647218</v>
+        <v>122647209</v>
       </c>
       <c r="B11" t="n">
-        <v>91125</v>
+        <v>82447</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551451</v>
+        <v>551421</v>
       </c>
       <c r="R11" t="n">
-        <v>7245990</v>
+        <v>7245967</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647222</v>
+        <v>122647232</v>
       </c>
       <c r="B12" t="n">
-        <v>57384</v>
+        <v>56594</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551481</v>
+        <v>551496</v>
       </c>
       <c r="R12" t="n">
-        <v>7246012</v>
+        <v>7246066</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hacskpår</t>
+          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647221</v>
+        <v>122647222</v>
       </c>
       <c r="B13" t="n">
-        <v>90852</v>
+        <v>57384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551452</v>
+        <v>551481</v>
       </c>
       <c r="R13" t="n">
-        <v>7246015</v>
+        <v>7246012</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,6 +1922,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1952,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647232</v>
+        <v>122647208</v>
       </c>
       <c r="B14" t="n">
-        <v>56594</v>
+        <v>91620</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1969,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>918</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551496</v>
+        <v>551419</v>
       </c>
       <c r="R14" t="n">
-        <v>7246066</v>
+        <v>7245952</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,11 +2033,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647207</v>
+        <v>122647221</v>
       </c>
       <c r="B15" t="n">
-        <v>90852</v>
+        <v>90855</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551407</v>
+        <v>551452</v>
       </c>
       <c r="R15" t="n">
-        <v>7245970</v>
+        <v>7246015</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647225</v>
+        <v>122647218</v>
       </c>
       <c r="B16" t="n">
-        <v>74758</v>
+        <v>91128</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,21 +2185,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551491</v>
+        <v>551451</v>
       </c>
       <c r="R16" t="n">
-        <v>7246031</v>
+        <v>7245990</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,7 +2278,7 @@
         <v>122647213</v>
       </c>
       <c r="B17" t="n">
-        <v>90830</v>
+        <v>90833</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647234</v>
+        <v>122647214</v>
       </c>
       <c r="B2" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551528</v>
+        <v>551447</v>
       </c>
       <c r="R2" t="n">
-        <v>7246053</v>
+        <v>7245973</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647223</v>
+        <v>122647213</v>
       </c>
       <c r="B3" t="n">
-        <v>78742</v>
+        <v>90833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551477</v>
+        <v>551412</v>
       </c>
       <c r="R3" t="n">
-        <v>7246026</v>
+        <v>7245972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647225</v>
+        <v>122647223</v>
       </c>
       <c r="B4" t="n">
-        <v>74761</v>
+        <v>78742</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551491</v>
+        <v>551477</v>
       </c>
       <c r="R4" t="n">
-        <v>7246031</v>
+        <v>7246026</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647224</v>
+        <v>122647208</v>
       </c>
       <c r="B5" t="n">
-        <v>78660</v>
+        <v>91620</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>918</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551488</v>
+        <v>551419</v>
       </c>
       <c r="R5" t="n">
-        <v>7246025</v>
+        <v>7245952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647207</v>
+        <v>122647222</v>
       </c>
       <c r="B6" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551407</v>
+        <v>551481</v>
       </c>
       <c r="R6" t="n">
-        <v>7245970</v>
+        <v>7246012</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,6 +1175,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647220</v>
+        <v>122647234</v>
       </c>
       <c r="B7" t="n">
-        <v>78742</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551458</v>
+        <v>551528</v>
       </c>
       <c r="R7" t="n">
-        <v>7245993</v>
+        <v>7246053</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647214</v>
+        <v>122647207</v>
       </c>
       <c r="B8" t="n">
-        <v>74761</v>
+        <v>90855</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551447</v>
+        <v>551407</v>
       </c>
       <c r="R8" t="n">
-        <v>7245973</v>
+        <v>7245970</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647233</v>
+        <v>122647218</v>
       </c>
       <c r="B9" t="n">
-        <v>90855</v>
+        <v>91128</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551495</v>
+        <v>551451</v>
       </c>
       <c r="R9" t="n">
-        <v>7246051</v>
+        <v>7245990</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647219</v>
+        <v>122647220</v>
       </c>
       <c r="B10" t="n">
-        <v>90837</v>
+        <v>78742</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551453</v>
+        <v>551458</v>
       </c>
       <c r="R10" t="n">
-        <v>7245978</v>
+        <v>7245993</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647209</v>
+        <v>122647224</v>
       </c>
       <c r="B11" t="n">
-        <v>82447</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551421</v>
+        <v>551488</v>
       </c>
       <c r="R11" t="n">
-        <v>7245967</v>
+        <v>7246025</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647232</v>
+        <v>122647233</v>
       </c>
       <c r="B12" t="n">
-        <v>56594</v>
+        <v>90855</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551496</v>
+        <v>551495</v>
       </c>
       <c r="R12" t="n">
-        <v>7246066</v>
+        <v>7246051</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,11 +1816,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647222</v>
+        <v>122647219</v>
       </c>
       <c r="B13" t="n">
-        <v>57384</v>
+        <v>90837</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551481</v>
+        <v>551453</v>
       </c>
       <c r="R13" t="n">
-        <v>7246012</v>
+        <v>7245978</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,11 +1922,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647208</v>
+        <v>122647221</v>
       </c>
       <c r="B14" t="n">
-        <v>91620</v>
+        <v>90855</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>918</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551419</v>
+        <v>551452</v>
       </c>
       <c r="R14" t="n">
-        <v>7245952</v>
+        <v>7246015</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647221</v>
+        <v>122647209</v>
       </c>
       <c r="B15" t="n">
-        <v>90855</v>
+        <v>82447</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,21 +2074,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551452</v>
+        <v>551421</v>
       </c>
       <c r="R15" t="n">
-        <v>7246015</v>
+        <v>7245967</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647218</v>
+        <v>122647232</v>
       </c>
       <c r="B16" t="n">
-        <v>91128</v>
+        <v>56594</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,25 +2176,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551451</v>
+        <v>551496</v>
       </c>
       <c r="R16" t="n">
-        <v>7245990</v>
+        <v>7246066</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,6 +2240,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647213</v>
+        <v>122647225</v>
       </c>
       <c r="B17" t="n">
-        <v>90833</v>
+        <v>74761</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551412</v>
+        <v>551491</v>
       </c>
       <c r="R17" t="n">
-        <v>7245972</v>
+        <v>7246031</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647214</v>
+        <v>122647207</v>
       </c>
       <c r="B2" t="n">
-        <v>74761</v>
+        <v>90958</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551447</v>
+        <v>551407</v>
       </c>
       <c r="R2" t="n">
-        <v>7245973</v>
+        <v>7245970</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647213</v>
+        <v>122647233</v>
       </c>
       <c r="B3" t="n">
-        <v>90833</v>
+        <v>90958</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551412</v>
+        <v>551495</v>
       </c>
       <c r="R3" t="n">
-        <v>7245972</v>
+        <v>7246051</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647223</v>
+        <v>122647221</v>
       </c>
       <c r="B4" t="n">
-        <v>78742</v>
+        <v>90958</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551477</v>
+        <v>551452</v>
       </c>
       <c r="R4" t="n">
-        <v>7246026</v>
+        <v>7246015</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647208</v>
+        <v>122647234</v>
       </c>
       <c r="B5" t="n">
-        <v>91620</v>
+        <v>78762</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>918</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551419</v>
+        <v>551528</v>
       </c>
       <c r="R5" t="n">
-        <v>7245952</v>
+        <v>7246053</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647222</v>
+        <v>122647218</v>
       </c>
       <c r="B6" t="n">
-        <v>57384</v>
+        <v>91231</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551481</v>
+        <v>551451</v>
       </c>
       <c r="R6" t="n">
-        <v>7246012</v>
+        <v>7245990</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,11 +1175,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647234</v>
+        <v>122647213</v>
       </c>
       <c r="B7" t="n">
-        <v>78660</v>
+        <v>90936</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551528</v>
+        <v>551412</v>
       </c>
       <c r="R7" t="n">
-        <v>7246053</v>
+        <v>7245972</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647207</v>
+        <v>122647219</v>
       </c>
       <c r="B8" t="n">
-        <v>90855</v>
+        <v>90940</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551407</v>
+        <v>551453</v>
       </c>
       <c r="R8" t="n">
-        <v>7245970</v>
+        <v>7245978</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647218</v>
+        <v>122647208</v>
       </c>
       <c r="B9" t="n">
-        <v>91128</v>
+        <v>91723</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>918</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551451</v>
+        <v>551419</v>
       </c>
       <c r="R9" t="n">
-        <v>7245990</v>
+        <v>7245952</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647220</v>
+        <v>122647222</v>
       </c>
       <c r="B10" t="n">
-        <v>78742</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551458</v>
+        <v>551481</v>
       </c>
       <c r="R10" t="n">
-        <v>7245993</v>
+        <v>7246012</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,6 +1599,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647224</v>
+        <v>122647225</v>
       </c>
       <c r="B11" t="n">
-        <v>78660</v>
+        <v>74863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551488</v>
+        <v>551491</v>
       </c>
       <c r="R11" t="n">
-        <v>7246025</v>
+        <v>7246031</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647233</v>
+        <v>122647214</v>
       </c>
       <c r="B12" t="n">
-        <v>90855</v>
+        <v>74863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551495</v>
+        <v>551447</v>
       </c>
       <c r="R12" t="n">
-        <v>7246051</v>
+        <v>7245973</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647219</v>
+        <v>122647209</v>
       </c>
       <c r="B13" t="n">
-        <v>90837</v>
+        <v>82549</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551453</v>
+        <v>551421</v>
       </c>
       <c r="R13" t="n">
-        <v>7245978</v>
+        <v>7245967</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647221</v>
+        <v>122647224</v>
       </c>
       <c r="B14" t="n">
-        <v>90855</v>
+        <v>78762</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551452</v>
+        <v>551488</v>
       </c>
       <c r="R14" t="n">
-        <v>7246015</v>
+        <v>7246025</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647209</v>
+        <v>122647232</v>
       </c>
       <c r="B15" t="n">
-        <v>82447</v>
+        <v>56688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,25 +2070,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551421</v>
+        <v>551496</v>
       </c>
       <c r="R15" t="n">
-        <v>7245967</v>
+        <v>7246066</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2134,6 +2134,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647232</v>
+        <v>122647223</v>
       </c>
       <c r="B16" t="n">
-        <v>56594</v>
+        <v>78844</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2181,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551496</v>
+        <v>551477</v>
       </c>
       <c r="R16" t="n">
-        <v>7246066</v>
+        <v>7246026</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,11 +2245,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647225</v>
+        <v>122647220</v>
       </c>
       <c r="B17" t="n">
-        <v>74761</v>
+        <v>78844</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551491</v>
+        <v>551458</v>
       </c>
       <c r="R17" t="n">
-        <v>7246031</v>
+        <v>7245993</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647219</v>
+        <v>122647222</v>
       </c>
       <c r="B8" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551453</v>
+        <v>551481</v>
       </c>
       <c r="R8" t="n">
-        <v>7245978</v>
+        <v>7246012</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,6 +1387,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647208</v>
+        <v>122647219</v>
       </c>
       <c r="B9" t="n">
-        <v>91723</v>
+        <v>90940</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>918</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551419</v>
+        <v>551453</v>
       </c>
       <c r="R9" t="n">
-        <v>7245952</v>
+        <v>7245978</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647222</v>
+        <v>122647208</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>91723</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>918</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551481</v>
+        <v>551419</v>
       </c>
       <c r="R10" t="n">
-        <v>7246012</v>
+        <v>7245952</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,11 +1604,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647207</v>
+        <v>122647220</v>
       </c>
       <c r="B2" t="n">
-        <v>90958</v>
+        <v>78848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551407</v>
+        <v>551458</v>
       </c>
       <c r="R2" t="n">
-        <v>7245970</v>
+        <v>7245993</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647233</v>
+        <v>122647223</v>
       </c>
       <c r="B3" t="n">
-        <v>90958</v>
+        <v>78848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551495</v>
+        <v>551477</v>
       </c>
       <c r="R3" t="n">
-        <v>7246051</v>
+        <v>7246026</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647221</v>
+        <v>122647233</v>
       </c>
       <c r="B4" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551452</v>
+        <v>551495</v>
       </c>
       <c r="R4" t="n">
-        <v>7246015</v>
+        <v>7246051</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647234</v>
+        <v>122647213</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
+        <v>90940</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551528</v>
+        <v>551412</v>
       </c>
       <c r="R5" t="n">
-        <v>7246053</v>
+        <v>7245972</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647218</v>
+        <v>122647224</v>
       </c>
       <c r="B6" t="n">
-        <v>91231</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551451</v>
+        <v>551488</v>
       </c>
       <c r="R6" t="n">
-        <v>7245990</v>
+        <v>7246025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647213</v>
+        <v>122647232</v>
       </c>
       <c r="B7" t="n">
-        <v>90936</v>
+        <v>56688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551412</v>
+        <v>551496</v>
       </c>
       <c r="R7" t="n">
-        <v>7245972</v>
+        <v>7246066</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647222</v>
+        <v>122647225</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551481</v>
+        <v>551491</v>
       </c>
       <c r="R8" t="n">
-        <v>7246012</v>
+        <v>7246031</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,11 +1392,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,7 +1425,7 @@
         <v>122647219</v>
       </c>
       <c r="B9" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647208</v>
+        <v>122647214</v>
       </c>
       <c r="B10" t="n">
-        <v>91723</v>
+        <v>74863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>918</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551419</v>
+        <v>551447</v>
       </c>
       <c r="R10" t="n">
-        <v>7245952</v>
+        <v>7245973</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647225</v>
+        <v>122647222</v>
       </c>
       <c r="B11" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551491</v>
+        <v>551481</v>
       </c>
       <c r="R11" t="n">
-        <v>7246031</v>
+        <v>7246012</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,6 +1710,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647214</v>
+        <v>122647218</v>
       </c>
       <c r="B12" t="n">
-        <v>74863</v>
+        <v>91235</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551447</v>
+        <v>551451</v>
       </c>
       <c r="R12" t="n">
-        <v>7245973</v>
+        <v>7245990</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647209</v>
+        <v>122647234</v>
       </c>
       <c r="B13" t="n">
-        <v>82549</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1867,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551421</v>
+        <v>551528</v>
       </c>
       <c r="R13" t="n">
-        <v>7245967</v>
+        <v>7246053</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647224</v>
+        <v>122647221</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
+        <v>90962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551488</v>
+        <v>551452</v>
       </c>
       <c r="R14" t="n">
-        <v>7246025</v>
+        <v>7246015</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647232</v>
+        <v>122647208</v>
       </c>
       <c r="B15" t="n">
-        <v>56688</v>
+        <v>91727</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,25 +2075,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>918</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551496</v>
+        <v>551419</v>
       </c>
       <c r="R15" t="n">
-        <v>7246066</v>
+        <v>7245952</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2134,11 +2139,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647223</v>
+        <v>122647207</v>
       </c>
       <c r="B16" t="n">
-        <v>78844</v>
+        <v>90962</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,21 +2185,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551477</v>
+        <v>551407</v>
       </c>
       <c r="R16" t="n">
-        <v>7246026</v>
+        <v>7245970</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647220</v>
+        <v>122647209</v>
       </c>
       <c r="B17" t="n">
-        <v>78844</v>
+        <v>82553</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551458</v>
+        <v>551421</v>
       </c>
       <c r="R17" t="n">
-        <v>7245993</v>
+        <v>7245967</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647220</v>
+        <v>122647207</v>
       </c>
       <c r="B2" t="n">
-        <v>78848</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551458</v>
+        <v>551407</v>
       </c>
       <c r="R2" t="n">
-        <v>7245993</v>
+        <v>7245970</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647223</v>
+        <v>122647225</v>
       </c>
       <c r="B3" t="n">
-        <v>78848</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551477</v>
+        <v>551491</v>
       </c>
       <c r="R3" t="n">
-        <v>7246026</v>
+        <v>7246031</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647233</v>
+        <v>122647232</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>56688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551495</v>
+        <v>551496</v>
       </c>
       <c r="R4" t="n">
-        <v>7246051</v>
+        <v>7246066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647213</v>
+        <v>122647221</v>
       </c>
       <c r="B5" t="n">
-        <v>90940</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551412</v>
+        <v>551452</v>
       </c>
       <c r="R5" t="n">
-        <v>7245972</v>
+        <v>7246015</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647224</v>
+        <v>122647222</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551488</v>
+        <v>551481</v>
       </c>
       <c r="R6" t="n">
-        <v>7246025</v>
+        <v>7246012</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,6 +1180,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647232</v>
+        <v>122647208</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>91727</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>918</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551496</v>
+        <v>551419</v>
       </c>
       <c r="R7" t="n">
-        <v>7246066</v>
+        <v>7245952</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1291,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647225</v>
+        <v>122647209</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551491</v>
+        <v>551421</v>
       </c>
       <c r="R8" t="n">
-        <v>7246031</v>
+        <v>7245967</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647219</v>
+        <v>122647234</v>
       </c>
       <c r="B9" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551453</v>
+        <v>551528</v>
       </c>
       <c r="R9" t="n">
-        <v>7245978</v>
+        <v>7246053</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1634,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647222</v>
+        <v>122647218</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>91235</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551481</v>
+        <v>551451</v>
       </c>
       <c r="R11" t="n">
-        <v>7246012</v>
+        <v>7245990</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647218</v>
+        <v>122647219</v>
       </c>
       <c r="B12" t="n">
-        <v>91235</v>
+        <v>90944</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551451</v>
+        <v>551453</v>
       </c>
       <c r="R12" t="n">
-        <v>7245990</v>
+        <v>7245978</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647234</v>
+        <v>122647233</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,21 +1867,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551528</v>
+        <v>551495</v>
       </c>
       <c r="R13" t="n">
-        <v>7246053</v>
+        <v>7246051</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647221</v>
+        <v>122647220</v>
       </c>
       <c r="B14" t="n">
-        <v>90962</v>
+        <v>78848</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551452</v>
+        <v>551458</v>
       </c>
       <c r="R14" t="n">
-        <v>7246015</v>
+        <v>7245993</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647208</v>
+        <v>122647224</v>
       </c>
       <c r="B15" t="n">
-        <v>91727</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2075,25 +2075,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>918</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551419</v>
+        <v>551488</v>
       </c>
       <c r="R15" t="n">
-        <v>7245952</v>
+        <v>7246025</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647207</v>
+        <v>122647213</v>
       </c>
       <c r="B16" t="n">
-        <v>90962</v>
+        <v>90940</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,21 +2185,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551407</v>
+        <v>551412</v>
       </c>
       <c r="R16" t="n">
-        <v>7245970</v>
+        <v>7245972</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647209</v>
+        <v>122647223</v>
       </c>
       <c r="B17" t="n">
-        <v>82553</v>
+        <v>78848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551421</v>
+        <v>551477</v>
       </c>
       <c r="R17" t="n">
-        <v>7245967</v>
+        <v>7246026</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647207</v>
+        <v>122647234</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551407</v>
+        <v>551528</v>
       </c>
       <c r="R2" t="n">
-        <v>7245970</v>
+        <v>7246053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647225</v>
+        <v>122647221</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551491</v>
+        <v>551452</v>
       </c>
       <c r="R3" t="n">
-        <v>7246031</v>
+        <v>7246015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647232</v>
+        <v>122647220</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>78848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551496</v>
+        <v>551458</v>
       </c>
       <c r="R4" t="n">
-        <v>7246066</v>
+        <v>7245993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647221</v>
+        <v>122647208</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>91727</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>918</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551452</v>
+        <v>551419</v>
       </c>
       <c r="R5" t="n">
-        <v>7246015</v>
+        <v>7245952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647222</v>
+        <v>122647207</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551481</v>
+        <v>551407</v>
       </c>
       <c r="R6" t="n">
-        <v>7246012</v>
+        <v>7245970</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,11 +1175,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647208</v>
+        <v>122647218</v>
       </c>
       <c r="B7" t="n">
-        <v>91727</v>
+        <v>91235</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>918</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551419</v>
+        <v>551451</v>
       </c>
       <c r="R7" t="n">
-        <v>7245952</v>
+        <v>7245990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647209</v>
+        <v>122647223</v>
       </c>
       <c r="B8" t="n">
-        <v>82553</v>
+        <v>78848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551421</v>
+        <v>551477</v>
       </c>
       <c r="R8" t="n">
-        <v>7245967</v>
+        <v>7246026</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647234</v>
+        <v>122647219</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551528</v>
+        <v>551453</v>
       </c>
       <c r="R9" t="n">
-        <v>7246053</v>
+        <v>7245978</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647214</v>
+        <v>122647225</v>
       </c>
       <c r="B10" t="n">
         <v>74863</v>
@@ -1573,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551447</v>
+        <v>551491</v>
       </c>
       <c r="R10" t="n">
-        <v>7245973</v>
+        <v>7246031</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647218</v>
+        <v>122647233</v>
       </c>
       <c r="B11" t="n">
-        <v>91235</v>
+        <v>90962</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551451</v>
+        <v>551495</v>
       </c>
       <c r="R11" t="n">
-        <v>7245990</v>
+        <v>7246051</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647219</v>
+        <v>122647224</v>
       </c>
       <c r="B12" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551453</v>
+        <v>551488</v>
       </c>
       <c r="R12" t="n">
-        <v>7245978</v>
+        <v>7246025</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647233</v>
+        <v>122647214</v>
       </c>
       <c r="B13" t="n">
-        <v>90962</v>
+        <v>74863</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551495</v>
+        <v>551447</v>
       </c>
       <c r="R13" t="n">
-        <v>7246051</v>
+        <v>7245973</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647220</v>
+        <v>122647209</v>
       </c>
       <c r="B14" t="n">
-        <v>78848</v>
+        <v>82553</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551458</v>
+        <v>551421</v>
       </c>
       <c r="R14" t="n">
-        <v>7245993</v>
+        <v>7245967</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647224</v>
+        <v>122647232</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2075,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551488</v>
+        <v>551496</v>
       </c>
       <c r="R15" t="n">
-        <v>7246025</v>
+        <v>7246066</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,6 +2129,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647223</v>
+        <v>122647222</v>
       </c>
       <c r="B17" t="n">
-        <v>78848</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551477</v>
+        <v>551481</v>
       </c>
       <c r="R17" t="n">
-        <v>7246026</v>
+        <v>7246012</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,6 +2346,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647207</v>
+        <v>122647218</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>91235</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551407</v>
+        <v>551451</v>
       </c>
       <c r="R6" t="n">
-        <v>7245970</v>
+        <v>7245990</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647218</v>
+        <v>122647207</v>
       </c>
       <c r="B7" t="n">
-        <v>91235</v>
+        <v>90962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551451</v>
+        <v>551407</v>
       </c>
       <c r="R7" t="n">
-        <v>7245990</v>
+        <v>7245970</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647234</v>
+        <v>122647225</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551528</v>
+        <v>551491</v>
       </c>
       <c r="R2" t="n">
-        <v>7246053</v>
+        <v>7246031</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647221</v>
+        <v>122647224</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551452</v>
+        <v>551488</v>
       </c>
       <c r="R3" t="n">
-        <v>7246015</v>
+        <v>7246025</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647220</v>
+        <v>122647207</v>
       </c>
       <c r="B4" t="n">
-        <v>78848</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551458</v>
+        <v>551407</v>
       </c>
       <c r="R4" t="n">
-        <v>7245993</v>
+        <v>7245970</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647208</v>
+        <v>122647221</v>
       </c>
       <c r="B5" t="n">
-        <v>91727</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>918</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551419</v>
+        <v>551452</v>
       </c>
       <c r="R5" t="n">
-        <v>7245952</v>
+        <v>7246015</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647218</v>
+        <v>122647233</v>
       </c>
       <c r="B6" t="n">
-        <v>91235</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551451</v>
+        <v>551495</v>
       </c>
       <c r="R6" t="n">
-        <v>7245990</v>
+        <v>7246051</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647207</v>
+        <v>122647219</v>
       </c>
       <c r="B7" t="n">
-        <v>90962</v>
+        <v>90944</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551407</v>
+        <v>551453</v>
       </c>
       <c r="R7" t="n">
-        <v>7245970</v>
+        <v>7245978</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647223</v>
+        <v>122647222</v>
       </c>
       <c r="B8" t="n">
-        <v>78848</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551477</v>
+        <v>551481</v>
       </c>
       <c r="R8" t="n">
-        <v>7246026</v>
+        <v>7246012</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,6 +1387,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647219</v>
+        <v>122647223</v>
       </c>
       <c r="B9" t="n">
-        <v>90944</v>
+        <v>78848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551453</v>
+        <v>551477</v>
       </c>
       <c r="R9" t="n">
-        <v>7245978</v>
+        <v>7246026</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647225</v>
+        <v>122647213</v>
       </c>
       <c r="B10" t="n">
-        <v>74863</v>
+        <v>90940</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551491</v>
+        <v>551412</v>
       </c>
       <c r="R10" t="n">
-        <v>7246031</v>
+        <v>7245972</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647233</v>
+        <v>122647214</v>
       </c>
       <c r="B11" t="n">
-        <v>90962</v>
+        <v>74863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551495</v>
+        <v>551447</v>
       </c>
       <c r="R11" t="n">
-        <v>7246051</v>
+        <v>7245973</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647224</v>
+        <v>122647234</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551488</v>
+        <v>551528</v>
       </c>
       <c r="R12" t="n">
-        <v>7246025</v>
+        <v>7246053</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647214</v>
+        <v>122647209</v>
       </c>
       <c r="B13" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551447</v>
+        <v>551421</v>
       </c>
       <c r="R13" t="n">
-        <v>7245973</v>
+        <v>7245967</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647209</v>
+        <v>122647218</v>
       </c>
       <c r="B14" t="n">
-        <v>82553</v>
+        <v>91235</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1968,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551421</v>
+        <v>551451</v>
       </c>
       <c r="R14" t="n">
-        <v>7245967</v>
+        <v>7245990</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647232</v>
+        <v>122647208</v>
       </c>
       <c r="B15" t="n">
-        <v>56688</v>
+        <v>91727</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2070,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>918</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551496</v>
+        <v>551419</v>
       </c>
       <c r="R15" t="n">
-        <v>7246066</v>
+        <v>7245952</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,11 +2134,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647213</v>
+        <v>122647232</v>
       </c>
       <c r="B16" t="n">
-        <v>90940</v>
+        <v>56688</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2176,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551412</v>
+        <v>551496</v>
       </c>
       <c r="R16" t="n">
-        <v>7245972</v>
+        <v>7246066</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,6 +2240,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647222</v>
+        <v>122647220</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>78848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551481</v>
+        <v>551458</v>
       </c>
       <c r="R17" t="n">
-        <v>7246012</v>
+        <v>7245993</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,11 +2351,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647225</v>
+        <v>122647224</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551491</v>
+        <v>551488</v>
       </c>
       <c r="R2" t="n">
-        <v>7246031</v>
+        <v>7246025</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647224</v>
+        <v>122647225</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551488</v>
+        <v>551491</v>
       </c>
       <c r="R3" t="n">
-        <v>7246025</v>
+        <v>7246031</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647222</v>
+        <v>122647223</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551481</v>
+        <v>551477</v>
       </c>
       <c r="R8" t="n">
-        <v>7246012</v>
+        <v>7246026</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,11 +1387,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647223</v>
+        <v>122647222</v>
       </c>
       <c r="B9" t="n">
-        <v>78848</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551477</v>
+        <v>551481</v>
       </c>
       <c r="R9" t="n">
-        <v>7246026</v>
+        <v>7246012</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,6 +1493,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647209</v>
+        <v>122647218</v>
       </c>
       <c r="B13" t="n">
-        <v>82553</v>
+        <v>91235</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551421</v>
+        <v>551451</v>
       </c>
       <c r="R13" t="n">
-        <v>7245967</v>
+        <v>7245990</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647218</v>
+        <v>122647209</v>
       </c>
       <c r="B14" t="n">
-        <v>91235</v>
+        <v>82553</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551451</v>
+        <v>551421</v>
       </c>
       <c r="R14" t="n">
-        <v>7245990</v>
+        <v>7245967</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647224</v>
+        <v>122647225</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551488</v>
+        <v>551491</v>
       </c>
       <c r="R2" t="n">
-        <v>7246025</v>
+        <v>7246031</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647225</v>
+        <v>122647224</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551491</v>
+        <v>551488</v>
       </c>
       <c r="R3" t="n">
-        <v>7246031</v>
+        <v>7246025</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647225</v>
+        <v>122647214</v>
       </c>
       <c r="B2" t="n">
         <v>74863</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551491</v>
+        <v>551447</v>
       </c>
       <c r="R2" t="n">
-        <v>7246031</v>
+        <v>7245973</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647224</v>
+        <v>122647207</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551488</v>
+        <v>551407</v>
       </c>
       <c r="R3" t="n">
-        <v>7246025</v>
+        <v>7245970</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647207</v>
+        <v>122647208</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>91735</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>918</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551407</v>
+        <v>551419</v>
       </c>
       <c r="R4" t="n">
-        <v>7245970</v>
+        <v>7245952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647221</v>
+        <v>122647232</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>56688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551452</v>
+        <v>551496</v>
       </c>
       <c r="R5" t="n">
-        <v>7246015</v>
+        <v>7246066</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647233</v>
+        <v>122647213</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>90948</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551495</v>
+        <v>551412</v>
       </c>
       <c r="R6" t="n">
-        <v>7246051</v>
+        <v>7245972</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647219</v>
+        <v>122647222</v>
       </c>
       <c r="B7" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551453</v>
+        <v>551481</v>
       </c>
       <c r="R7" t="n">
-        <v>7245978</v>
+        <v>7246012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647223</v>
+        <v>122647233</v>
       </c>
       <c r="B8" t="n">
-        <v>78848</v>
+        <v>90970</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551477</v>
+        <v>551495</v>
       </c>
       <c r="R8" t="n">
-        <v>7246026</v>
+        <v>7246051</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647222</v>
+        <v>122647219</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551481</v>
+        <v>551453</v>
       </c>
       <c r="R9" t="n">
-        <v>7246012</v>
+        <v>7245978</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,11 +1503,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647213</v>
+        <v>122647225</v>
       </c>
       <c r="B10" t="n">
-        <v>90940</v>
+        <v>74863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551412</v>
+        <v>551491</v>
       </c>
       <c r="R10" t="n">
-        <v>7245972</v>
+        <v>7246031</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647214</v>
+        <v>122647234</v>
       </c>
       <c r="B11" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551447</v>
+        <v>551528</v>
       </c>
       <c r="R11" t="n">
-        <v>7245973</v>
+        <v>7246053</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647234</v>
+        <v>122647209</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551528</v>
+        <v>551421</v>
       </c>
       <c r="R12" t="n">
-        <v>7246053</v>
+        <v>7245967</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,7 +1854,7 @@
         <v>122647218</v>
       </c>
       <c r="B13" t="n">
-        <v>91235</v>
+        <v>91243</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647209</v>
+        <v>122647220</v>
       </c>
       <c r="B14" t="n">
-        <v>82553</v>
+        <v>78848</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551421</v>
+        <v>551458</v>
       </c>
       <c r="R14" t="n">
-        <v>7245967</v>
+        <v>7245993</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647208</v>
+        <v>122647223</v>
       </c>
       <c r="B15" t="n">
-        <v>91727</v>
+        <v>78848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,25 +2075,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>918</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551419</v>
+        <v>551477</v>
       </c>
       <c r="R15" t="n">
-        <v>7245952</v>
+        <v>7246026</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647232</v>
+        <v>122647221</v>
       </c>
       <c r="B16" t="n">
-        <v>56688</v>
+        <v>90970</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2181,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551496</v>
+        <v>551452</v>
       </c>
       <c r="R16" t="n">
-        <v>7246066</v>
+        <v>7246015</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,11 +2245,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647220</v>
+        <v>122647224</v>
       </c>
       <c r="B17" t="n">
-        <v>78848</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551458</v>
+        <v>551488</v>
       </c>
       <c r="R17" t="n">
-        <v>7245993</v>
+        <v>7246025</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647214</v>
+        <v>122647223</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
+        <v>78845</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551447</v>
+        <v>551477</v>
       </c>
       <c r="R2" t="n">
-        <v>7245973</v>
+        <v>7246026</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647207</v>
+        <v>122647218</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>91243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551407</v>
+        <v>551451</v>
       </c>
       <c r="R3" t="n">
-        <v>7245970</v>
+        <v>7245990</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647208</v>
+        <v>122647225</v>
       </c>
       <c r="B4" t="n">
-        <v>91735</v>
+        <v>74863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>918</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551419</v>
+        <v>551491</v>
       </c>
       <c r="R4" t="n">
-        <v>7245952</v>
+        <v>7246031</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647232</v>
+        <v>122647233</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
+        <v>90970</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551496</v>
+        <v>551495</v>
       </c>
       <c r="R5" t="n">
-        <v>7246066</v>
+        <v>7246051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,11 +1069,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1321,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647233</v>
+        <v>122647208</v>
       </c>
       <c r="B8" t="n">
-        <v>90970</v>
+        <v>91735</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>918</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551495</v>
+        <v>551419</v>
       </c>
       <c r="R8" t="n">
-        <v>7246051</v>
+        <v>7245952</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647219</v>
+        <v>122647220</v>
       </c>
       <c r="B9" t="n">
-        <v>90952</v>
+        <v>78845</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551453</v>
+        <v>551458</v>
       </c>
       <c r="R9" t="n">
-        <v>7245978</v>
+        <v>7245993</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647225</v>
+        <v>122647219</v>
       </c>
       <c r="B10" t="n">
-        <v>74863</v>
+        <v>90952</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551491</v>
+        <v>551453</v>
       </c>
       <c r="R10" t="n">
-        <v>7246031</v>
+        <v>7245978</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647234</v>
+        <v>122647209</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551528</v>
+        <v>551421</v>
       </c>
       <c r="R11" t="n">
-        <v>7246053</v>
+        <v>7245967</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647209</v>
+        <v>122647234</v>
       </c>
       <c r="B12" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551421</v>
+        <v>551528</v>
       </c>
       <c r="R12" t="n">
-        <v>7245967</v>
+        <v>7246053</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647218</v>
+        <v>122647224</v>
       </c>
       <c r="B13" t="n">
-        <v>91243</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551451</v>
+        <v>551488</v>
       </c>
       <c r="R13" t="n">
-        <v>7245990</v>
+        <v>7246025</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647220</v>
+        <v>122647232</v>
       </c>
       <c r="B14" t="n">
-        <v>78848</v>
+        <v>56688</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551458</v>
+        <v>551496</v>
       </c>
       <c r="R14" t="n">
-        <v>7245993</v>
+        <v>7246066</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,6 +2028,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647223</v>
+        <v>122647221</v>
       </c>
       <c r="B15" t="n">
-        <v>78848</v>
+        <v>90970</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,21 +2079,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551477</v>
+        <v>551452</v>
       </c>
       <c r="R15" t="n">
-        <v>7246026</v>
+        <v>7246015</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,7 +2169,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647221</v>
+        <v>122647207</v>
       </c>
       <c r="B16" t="n">
         <v>90970</v>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551452</v>
+        <v>551407</v>
       </c>
       <c r="R16" t="n">
-        <v>7246015</v>
+        <v>7245970</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647224</v>
+        <v>122647214</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551488</v>
+        <v>551447</v>
       </c>
       <c r="R17" t="n">
-        <v>7246025</v>
+        <v>7245973</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647232</v>
+        <v>122647221</v>
       </c>
       <c r="B14" t="n">
-        <v>56688</v>
+        <v>90970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551496</v>
+        <v>551452</v>
       </c>
       <c r="R14" t="n">
-        <v>7246066</v>
+        <v>7246015</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,11 +2028,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647221</v>
+        <v>122647232</v>
       </c>
       <c r="B15" t="n">
-        <v>90970</v>
+        <v>56688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2075,25 +2070,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551452</v>
+        <v>551496</v>
       </c>
       <c r="R15" t="n">
-        <v>7246015</v>
+        <v>7246066</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,6 +2134,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 15340-2023 artfynd.xlsx
+++ b/artfynd/A 15340-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647223</v>
+        <v>122647219</v>
       </c>
       <c r="B2" t="n">
-        <v>78845</v>
+        <v>90952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551477</v>
+        <v>551453</v>
       </c>
       <c r="R2" t="n">
-        <v>7246026</v>
+        <v>7245978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647218</v>
+        <v>122647209</v>
       </c>
       <c r="B3" t="n">
-        <v>91243</v>
+        <v>82553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551451</v>
+        <v>551421</v>
       </c>
       <c r="R3" t="n">
-        <v>7245990</v>
+        <v>7245967</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647225</v>
+        <v>122647224</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551491</v>
+        <v>551488</v>
       </c>
       <c r="R4" t="n">
-        <v>7246031</v>
+        <v>7246025</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647233</v>
+        <v>122647223</v>
       </c>
       <c r="B5" t="n">
-        <v>90970</v>
+        <v>78845</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551495</v>
+        <v>551477</v>
       </c>
       <c r="R5" t="n">
-        <v>7246051</v>
+        <v>7246026</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647222</v>
+        <v>122647232</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551481</v>
+        <v>551496</v>
       </c>
       <c r="R7" t="n">
-        <v>7246012</v>
+        <v>7246066</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hacskpår</t>
+          <t>Hane, uppflög</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647208</v>
+        <v>122647225</v>
       </c>
       <c r="B8" t="n">
-        <v>91735</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>918</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551419</v>
+        <v>551491</v>
       </c>
       <c r="R8" t="n">
-        <v>7245952</v>
+        <v>7246031</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647220</v>
+        <v>122647221</v>
       </c>
       <c r="B9" t="n">
-        <v>78845</v>
+        <v>90970</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551458</v>
+        <v>551452</v>
       </c>
       <c r="R9" t="n">
-        <v>7245993</v>
+        <v>7246015</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647219</v>
+        <v>122647233</v>
       </c>
       <c r="B10" t="n">
-        <v>90952</v>
+        <v>90970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551453</v>
+        <v>551495</v>
       </c>
       <c r="R10" t="n">
-        <v>7245978</v>
+        <v>7246051</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647209</v>
+        <v>122647218</v>
       </c>
       <c r="B11" t="n">
-        <v>82553</v>
+        <v>91243</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551421</v>
+        <v>551451</v>
       </c>
       <c r="R11" t="n">
-        <v>7245967</v>
+        <v>7245990</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647234</v>
+        <v>122647208</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>91735</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>918</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551528</v>
+        <v>551419</v>
       </c>
       <c r="R12" t="n">
-        <v>7246053</v>
+        <v>7245952</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,7 +1846,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647224</v>
+        <v>122647234</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551488</v>
+        <v>551528</v>
       </c>
       <c r="R13" t="n">
-        <v>7246025</v>
+        <v>7246053</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647221</v>
+        <v>122647220</v>
       </c>
       <c r="B14" t="n">
-        <v>90970</v>
+        <v>78845</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551452</v>
+        <v>551458</v>
       </c>
       <c r="R14" t="n">
-        <v>7246015</v>
+        <v>7245993</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647232</v>
+        <v>122647222</v>
       </c>
       <c r="B15" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,25 +2070,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551496</v>
+        <v>551481</v>
       </c>
       <c r="R15" t="n">
-        <v>7246066</v>
+        <v>7246012</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hane, uppflög</t>
+          <t>Hacskpår</t>
         </is>
       </c>
       <c r="AD15" t="b">
